--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF96D04A-8CFD-4D95-89C7-B1AFB0AA401B}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7D731D-CAAE-4CB3-9CF8-4E350C7F788D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -167,13 +167,39 @@
   </si>
   <si>
     <t>https://link.springer.com/chapter/10.1007/978-3-032-04496-9_13</t>
+  </si>
+  <si>
+    <t>working-paper</t>
+  </si>
+  <si>
+    <t>Preprint</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=5728066</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=5549219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoš, M., Horák, F., Jelínek, F., Preuss, O. </t>
+  </si>
+  <si>
+    <t>This case note analyses a landmark judgment of the Czech Constitutional Court in which the Court halted the ratification of a concordat concluded between the Czech Republic and the Holy See, declaring two substantive treaty provisions incompatible with the constitutional order. The Court found that an absolute recognition of the seal of confession and a provision allowing church legal entities to unilaterally determine conditions of access to cultural heritage amounted to unjustified treaty‑based privileges incompatible with principles of religious neutrality and equality.
+Beyond reconstructing the majority and dissenting opinions, the note develops a structured analytical framework for assessing the constitutionality of concordat‑type treaties. It identifies a set of interacting factors, including the presence of self‑executing treaty provisions, their priority in monist legal orders, the absence of domestic specification clauses, and the procedural implications of ex ante constitutional review. The analysis further reconstructs the Court’s test of religious neutrality and situates it within a broader spectrum of constitutional models of church–state relations.
+While grounded in Czech constitutional law, the note argues that the judgment exposes structural tensions relevant to other constitutional systems confronting treaty‑based religious privileges. It thus offers analytical tools of comparative interest for courts and scholars working at the intersection of religious freedom, constitutional neutrality, and the domestic effects of international treaties.</t>
+  </si>
+  <si>
+    <t>Religious Neutrality and Treaty-Based Privileges: The Czech Constitutional Court on the Holy See Concordat</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6717161</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,11 +211,19 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -203,7 +237,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -226,12 +260,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -240,6 +285,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -543,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.88671875" customWidth="1"/>
@@ -554,7 +602,7 @@
     <col min="7" max="7" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,8 +633,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -618,7 +669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -649,8 +700,11 @@
       <c r="J3" t="s">
         <v>23</v>
       </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -682,7 +736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -714,7 +768,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -739,19 +793,55 @@
       <c r="H6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7">
+        <v>2026</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{E36AC91E-386B-4DDC-B4B4-D8D3D62E3A5D}"/>
     <hyperlink ref="I5" r:id="rId2" xr:uid="{BF901E71-545E-468E-BD6C-66136992B469}"/>
     <hyperlink ref="J5" r:id="rId3" xr:uid="{39C47766-1FCA-45B1-BE70-6C58868C6E50}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{FB8735BA-A79F-4ACD-B69F-43FA534B1BEC}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{232950F9-4DCB-4573-8256-8B383B0BA762}"/>
+    <hyperlink ref="K6" r:id="rId6" display="https://papers.ssrn.com/sol3/papers.cfm?abstract_id=5728065" xr:uid="{341D9E15-40FC-4D09-95B4-C7AA0A7551BC}"/>
+    <hyperlink ref="J7" r:id="rId7" xr:uid="{6353FAE5-977D-4D4F-9691-BAC42FC55F2E}"/>
+    <hyperlink ref="K7" r:id="rId8" xr:uid="{7D8744DE-2AF3-4CA5-B6ED-04AE042FF3E6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>
--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7D731D-CAAE-4CB3-9CF8-4E350C7F788D}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4464FC6A-ACB0-4503-9F31-681EDDF96AC4}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>id</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6717161</t>
+  </si>
+  <si>
+    <t>pub-religious-neutral-priv</t>
   </si>
 </sst>
 </file>
@@ -804,6 +807,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>54</v>
       </c>

--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4464FC6A-ACB0-4503-9F31-681EDDF96AC4}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37CC60CF-43C9-4D1A-AC47-20D2FAA503D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -196,6 +196,12 @@
   </si>
   <si>
     <t>pub-religious-neutral-priv</t>
+  </si>
+  <si>
+    <t>replication</t>
+  </si>
+  <si>
+    <t>OSF | Mandatory vaccination policies</t>
   </si>
 </sst>
 </file>
@@ -279,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -289,6 +295,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -594,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.88671875" customWidth="1"/>
@@ -605,7 +614,7 @@
     <col min="7" max="7" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -639,8 +648,11 @@
       <c r="K1" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -671,8 +683,11 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -707,7 +722,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -739,7 +754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -771,7 +786,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -806,7 +821,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>56</v>
       </c>

--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37CC60CF-43C9-4D1A-AC47-20D2FAA503D4}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10EF4861-E683-4227-B14B-EBB053F8CE36}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>replication</t>
-  </si>
-  <si>
-    <t>OSF | Mandatory vaccination policies</t>
   </si>
 </sst>
 </file>
@@ -285,7 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -295,9 +292,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -648,7 +642,7 @@
       <c r="K1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>57</v>
       </c>
     </row>
@@ -680,11 +674,11 @@
       <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
-        <v>58</v>
+      <c r="L2" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -861,8 +855,10 @@
     <hyperlink ref="K6" r:id="rId6" display="https://papers.ssrn.com/sol3/papers.cfm?abstract_id=5728065" xr:uid="{341D9E15-40FC-4D09-95B4-C7AA0A7551BC}"/>
     <hyperlink ref="J7" r:id="rId7" xr:uid="{6353FAE5-977D-4D4F-9691-BAC42FC55F2E}"/>
     <hyperlink ref="K7" r:id="rId8" xr:uid="{7D8744DE-2AF3-4CA5-B6ED-04AE042FF3E6}"/>
+    <hyperlink ref="J2" r:id="rId9" xr:uid="{7307ECA8-6274-48F5-B26A-21833AE98DF2}"/>
+    <hyperlink ref="L2" r:id="rId10" xr:uid="{413A8BC1-6C1C-437F-A3F1-D99A145C19DB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>
--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10EF4861-E683-4227-B14B-EBB053F8CE36}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA8DCF79-EEA6-4F30-955D-471A0AF3D455}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>id</t>
   </si>
@@ -199,13 +199,25 @@
   </si>
   <si>
     <t>replication</t>
+  </si>
+  <si>
+    <t>Interlegal Reasoning and Judicial Minimalism</t>
+  </si>
+  <si>
+    <t>The current academic literature on the benefits of minimalist reasoning in judicial proceedings presents this technique as promoting democratic decision-making and dialogue between the legislature and the judiciary. In this chapter, I will try to demonstrate that the same arguments can be used in a situation of dialogue between different courts in a pluralistic legal order and in a situation of interlegal reasoning. Therefore, the aim of this chapter is to demonstrate, using concrete and hypothetical examples, that minimalist reasoning can strengthen the argumentative position of an individual seeking to vindicate his or her rights in a situation of pluralistic interaction between different legal systems.</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/chapter/10.1007/978-3-032-22525-2_6</t>
+  </si>
+  <si>
+    <t>pub-interlegal-reason</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +245,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -282,7 +301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -294,6 +313,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -597,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.88671875" customWidth="1"/>
@@ -842,6 +862,35 @@
       </c>
       <c r="K7" s="3" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>2026</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA8DCF79-EEA6-4F30-955D-471A0AF3D455}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC538761-B2F6-454F-9BEE-5971D06AFB61}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28905" yWindow="-4080" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
   <si>
     <t>id</t>
   </si>
@@ -211,6 +211,57 @@
   </si>
   <si>
     <t>pub-interlegal-reason</t>
+  </si>
+  <si>
+    <t>This paper leverages the staggered timing in NYC hotel-to-migrant shelter conversions to identify a potential "native flight" mechanism in housing and rental markets. Estimates from a difference-in-differences specification show no evidence of native flight in Zillow market indicators, even in neighborhoods with the highest concentrations of non-Hispanic White residents. A complementary proximity-based analysis likewise finds that property sales prices were unaffected by shocks to the local migrant population.</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6447258</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6447260</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6447261</t>
+  </si>
+  <si>
+    <t>LeRoy, W.</t>
+  </si>
+  <si>
+    <t>Do Migrant Shelter Hotels Cause "Native Flight"?: Evidence from NYC Housing Markets</t>
+  </si>
+  <si>
+    <t>pub-migrant-shelter-nyc</t>
+  </si>
+  <si>
+    <t>Bon Débarras ?: Small Boat Migrant Crossings of the English Channel and French Crime Rates</t>
+  </si>
+  <si>
+    <t>pub-boatcrossing-crime-fr</t>
+  </si>
+  <si>
+    <t>This paper tests whether small boat migrant crossings of the English Channel lowered crime rates in communes near the northern French coast relative to inland communes. Conditioning on mainland weather, I instrument annual small boat out-migration using the number of days with a greater than 55% likelihood of "small boat activity," as determined by the Met Office using forecasted wave height, among other factors, in the Dover Strait. There is no evidence of a crime reduction, even when restricting attention to the poorest and most overcrowded communes.</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6571279</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6571280</t>
+  </si>
+  <si>
+    <t>This paper examines dynamic beliefs about peace in the wake of violent conflict during the Israel-Hamas war. I leverage the staggered timing in the roll-out of the Israel National Election Studies survey, relative to the breakdown of a two-month-long ceasefire in March 2025, in a difference-in-differences specification for estimation. I find a short-lived effect, ranging from a 4.19 to 8.38 percentage point decline, in respondents' beliefs that peace is possible. I attribute the baseline result to group-level social identity, with respondents who do not directly know someone harmed by Hamas driving the effect. I rule out other forms of social cohesion, including eroding trust in leadership and cooperation via political protest, as well as alternative explanations such as changes in media consumption and/or issue prioritization around the breakdown of the ceasefire.</t>
+  </si>
+  <si>
+    <t>The Breakdown of a Ceasefire: Evidence on Dynamic Beliefs About Peace in the Israel-Hamas War</t>
+  </si>
+  <si>
+    <t>pub-ceasefire-dynamic-beliefs</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6823339</t>
+  </si>
+  <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6823340</t>
   </si>
 </sst>
 </file>
@@ -617,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.88671875" customWidth="1"/>
@@ -891,6 +942,102 @@
       </c>
       <c r="J8" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>2026</v>
+      </c>
+      <c r="G9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>2026</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11">
+        <v>2026</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC538761-B2F6-454F-9BEE-5971D06AFB61}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="11_2B59D2BFD360D54D4B392611596098767B8FE680" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F8E9094-E74F-41DB-AA8B-63117F8A4B2D}"/>
   <bookViews>
     <workbookView xWindow="-28905" yWindow="-4080" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="87">
   <si>
     <t>id</t>
   </si>
@@ -262,6 +262,30 @@
   </si>
   <si>
     <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6823340</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>pub-macroprudential-policy</t>
+  </si>
+  <si>
+    <t>Macroprudential Policy and Income Inequality: The Trade-Off Between Crisis Prevention and Credit Redistribution</t>
+  </si>
+  <si>
+    <t>Malovaná, S., Janků, J., Hodula, M.</t>
+  </si>
+  <si>
+    <t>International Journal of Central Banking</t>
+  </si>
+  <si>
+    <t>Using data on 105 countries from 1990 to 2019 and a lag-augmented local projection method, we document that macroprudential policy tightening affects income inequality through two key channels: the crisis mitigation and prevention channel and the credit redistribution channel. Through the first of these, tighter regulation during credit booms reduces income inequality and mitigates the redistributive effects of financial crises, reflecting the enhanced financial sector’s resilience. Through the second, it contributes to higher inequality due to its negative effect on credit growth and property prices. This has important policy implications: the timely implementation of macroprudential regulation has preventive effects and can contribute to a more equal distribution of society’s income.</t>
+  </si>
+  <si>
+    <t>https://www.ijcb.org/journal/v21n4/macroprudential-policy-and-income-inequality-trade-between-crisis-prevention-and</t>
+  </si>
+  <si>
+    <t>https://www.cnb.cz/en/economic-research/research-publications/cnb-working-paper-series/Macroprudential-Policy-and-Income-Inequality-The-Trade-off-Between-Crisis-Prevention-and-Credit-Redistribution-00001/</t>
   </si>
 </sst>
 </file>
@@ -668,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.88671875" customWidth="1"/>
@@ -960,6 +984,9 @@
       <c r="E9">
         <v>2026</v>
       </c>
+      <c r="F9" t="s">
+        <v>79</v>
+      </c>
       <c r="G9" t="s">
         <v>62</v>
       </c>
@@ -992,6 +1019,9 @@
       <c r="E10">
         <v>2026</v>
       </c>
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
       <c r="G10" s="2" t="s">
         <v>71</v>
       </c>
@@ -1024,6 +1054,9 @@
       <c r="E11">
         <v>2026</v>
       </c>
+      <c r="F11" t="s">
+        <v>79</v>
+      </c>
       <c r="G11" s="2" t="s">
         <v>74</v>
       </c>
@@ -1038,6 +1071,41 @@
       </c>
       <c r="L11" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>2025</v>
+      </c>
+      <c r="F12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
